--- a/data/trans_dic/P16A13-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,17</t>
+          <t>1,0; 4,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,36</t>
+          <t>3,59; 10,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,15</t>
+          <t>1,36; 5,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 12,71</t>
+          <t>3,76; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,4</t>
+          <t>1,13; 5,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,3</t>
+          <t>3,94; 9,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,8</t>
+          <t>4,77; 12,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,71</t>
+          <t>3,06; 6,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,56</t>
+          <t>1,47; 4,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,79</t>
+          <t>4,61; 8,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,7</t>
+          <t>3,89; 7,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,94</t>
+          <t>3,77; 8,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,34</t>
+          <t>2,08; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,84</t>
+          <t>3,58; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,96</t>
+          <t>1,18; 3,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,43</t>
+          <t>1,21; 4,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,65</t>
+          <t>2,4; 5,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,77</t>
+          <t>4,13; 8,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,16</t>
+          <t>0,76; 3,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,91</t>
+          <t>2,09; 4,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,16</t>
+          <t>2,59; 5,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,31</t>
+          <t>4,36; 7,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,88</t>
+          <t>1,17; 3,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,14</t>
+          <t>2,04; 4,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,38</t>
+          <t>0,61; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,9</t>
+          <t>1,88; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,04</t>
+          <t>0,65; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 13,61</t>
+          <t>7,88; 13,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,24</t>
+          <t>1,98; 6,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,29</t>
+          <t>2,24; 6,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,61</t>
+          <t>0,7; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 19,03</t>
+          <t>13,2; 19,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,1</t>
+          <t>1,58; 4,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,68</t>
+          <t>2,5; 5,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,15</t>
+          <t>1,1; 3,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,78</t>
+          <t>11,23; 15,65</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,11</t>
+          <t>0,8; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,59</t>
+          <t>1,05; 4,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,23</t>
+          <t>2,73; 7,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,45</t>
+          <t>4,14; 9,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,65</t>
+          <t>2,55; 6,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,84</t>
+          <t>5,5; 10,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,21</t>
+          <t>4,91; 11,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,62</t>
+          <t>4,94; 10,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,59</t>
+          <t>2,07; 4,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,08</t>
+          <t>3,59; 6,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,15</t>
+          <t>4,44; 8,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,17</t>
+          <t>5,06; 9,25</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,86</t>
+          <t>0,44; 4,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,7</t>
+          <t>4,86; 12,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,08</t>
+          <t>0,45; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,32</t>
+          <t>9,73; 17,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,33</t>
+          <t>1,89; 7,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,45</t>
+          <t>4,22; 11,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,93; 24,91</t>
+          <t>17,79; 24,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,14</t>
+          <t>1,6; 5,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,69</t>
+          <t>5,25; 10,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,46</t>
+          <t>1,22; 4,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,9; 20,33</t>
+          <t>14,93; 20,22</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,15</t>
+          <t>0,71; 4,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,98</t>
+          <t>2,85; 8,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,87</t>
+          <t>1,5; 5,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,23</t>
+          <t>11,15; 17,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,37</t>
+          <t>2,22; 7,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,71</t>
+          <t>2,08; 6,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,41</t>
+          <t>0,91; 4,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,97; 18,94</t>
+          <t>13,03; 19,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,84</t>
+          <t>1,86; 4,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,73</t>
+          <t>3,08; 6,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,58</t>
+          <t>1,62; 4,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,59; 17,35</t>
+          <t>12,77; 17,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,93</t>
+          <t>1,84; 4,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,27</t>
+          <t>2,23; 5,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,68</t>
+          <t>2,44; 5,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,93</t>
+          <t>4,09; 7,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,52</t>
+          <t>3,25; 6,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,46</t>
+          <t>3,67; 7,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,1</t>
+          <t>3,4; 7,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,07</t>
+          <t>3,14; 9,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,1</t>
+          <t>2,94; 5,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,82</t>
+          <t>3,28; 5,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,78</t>
+          <t>3,27; 5,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,67</t>
+          <t>3,81; 7,73</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,44</t>
+          <t>1,92; 4,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,03</t>
+          <t>1,56; 4,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,17</t>
+          <t>1,59; 4,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,28</t>
+          <t>1,01; 4,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,62</t>
+          <t>1,32; 3,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,78</t>
+          <t>2,74; 5,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,86</t>
+          <t>2,15; 4,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,14</t>
+          <t>2,07; 4,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,63</t>
+          <t>1,87; 3,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,49</t>
+          <t>2,39; 4,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,94</t>
+          <t>2,23; 4,1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,73</t>
+          <t>1,68; 3,78</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,15; 3,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,87</t>
+          <t>3,43; 4,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,61</t>
+          <t>2,36; 3,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,97</t>
+          <t>4,55; 6,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,21</t>
+          <t>3,01; 4,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,23</t>
+          <t>4,59; 6,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,83</t>
+          <t>3,44; 4,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,69</t>
+          <t>6,44; 8,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,53</t>
+          <t>2,72; 3,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,31</t>
+          <t>4,26; 5,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,98</t>
+          <t>3,05; 4,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,63</t>
+          <t>6,02; 7,58</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2783; 14125</t>
+          <t>2732; 13630</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10668; 30078</t>
+          <t>10429; 29488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3946; 15143</t>
+          <t>3996; 15273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11247; 39571</t>
+          <t>11708; 44663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3038; 14080</t>
+          <t>2960; 13619</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11289; 28962</t>
+          <t>11095; 27943</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14773; 34070</t>
+          <t>13759; 35326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8898; 19424</t>
+          <t>8873; 19534</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8552; 24350</t>
+          <t>7864; 23651</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24990; 50224</t>
+          <t>26325; 51123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22150; 44837</t>
+          <t>22659; 45845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23190; 53717</t>
+          <t>22659; 51264</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10366; 26306</t>
+          <t>10274; 27393</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17595; 39627</t>
+          <t>18079; 38303</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5882; 19902</t>
+          <t>5907; 19305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6406; 22911</t>
+          <t>6249; 22931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11975; 28474</t>
+          <t>12112; 28058</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22054; 45854</t>
+          <t>21576; 45053</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3969; 16513</t>
+          <t>3986; 16732</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11191; 25210</t>
+          <t>10754; 25033</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25811; 51443</t>
+          <t>25832; 50979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43911; 75134</t>
+          <t>44860; 75842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10783; 29528</t>
+          <t>12037; 31427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21263; 42688</t>
+          <t>21081; 42421</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1916; 10784</t>
+          <t>1942; 11500</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5046; 22287</t>
+          <t>6063; 23103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2775; 12870</t>
+          <t>2057; 12537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24933; 43005</t>
+          <t>24908; 43264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6475; 20934</t>
+          <t>6626; 20482</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7203; 21452</t>
+          <t>7641; 22364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2636; 12155</t>
+          <t>2361; 13431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46775; 66443</t>
+          <t>46095; 66675</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10351; 26808</t>
+          <t>10321; 26423</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15870; 37747</t>
+          <t>16584; 39154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6567; 20633</t>
+          <t>7209; 21235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75750; 104935</t>
+          <t>74688; 104127</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2944; 14744</t>
+          <t>2865; 14291</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3925; 17184</t>
+          <t>3928; 17216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9888; 26734</t>
+          <t>10108; 27681</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12719; 29546</t>
+          <t>12926; 28129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9853; 24708</t>
+          <t>9476; 23716</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21237; 42058</t>
+          <t>21341; 41931</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19706; 43414</t>
+          <t>19023; 44068</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22947; 50509</t>
+          <t>23504; 51111</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14837; 33513</t>
+          <t>15130; 33504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29114; 53969</t>
+          <t>27318; 52626</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34057; 61751</t>
+          <t>33612; 62581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41111; 72276</t>
+          <t>39913; 72934</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1604; 9888</t>
+          <t>894; 9147</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10570; 27006</t>
+          <t>10324; 26343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>941; 8611</t>
+          <t>948; 8963</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17599; 30950</t>
+          <t>17390; 31788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3890; 15222</t>
+          <t>3935; 16091</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8702; 25136</t>
+          <t>9265; 24901</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2983; 14266</t>
+          <t>2972; 14275</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37418; 51980</t>
+          <t>37130; 51852</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6639; 21115</t>
+          <t>6568; 20776</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21695; 46183</t>
+          <t>22690; 46551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5126; 19189</t>
+          <t>5225; 17582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57733; 78773</t>
+          <t>57847; 78347</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1916; 11238</t>
+          <t>1932; 11013</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8443; 24614</t>
+          <t>7805; 23725</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4253; 15435</t>
+          <t>3942; 14840</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29967; 46452</t>
+          <t>30076; 47240</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6295; 20506</t>
+          <t>6181; 19767</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5909; 18740</t>
+          <t>5818; 18833</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2847; 14771</t>
+          <t>2472; 13255</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33331; 48694</t>
+          <t>33501; 49711</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9686; 26568</t>
+          <t>10230; 26254</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16491; 37238</t>
+          <t>17029; 37299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8805; 24561</t>
+          <t>8673; 24205</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>66292; 91406</t>
+          <t>67242; 91612</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11480; 30345</t>
+          <t>11318; 29170</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13989; 34839</t>
+          <t>14758; 34894</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16118; 37291</t>
+          <t>16050; 38678</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25787; 49526</t>
+          <t>25509; 48122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20948; 41585</t>
+          <t>20769; 42169</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25680; 51774</t>
+          <t>25488; 51526</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23157; 49083</t>
+          <t>23479; 48960</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28421; 77014</t>
+          <t>26698; 76670</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36446; 63895</t>
+          <t>36857; 63268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45116; 78800</t>
+          <t>44423; 79063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44365; 77948</t>
+          <t>44073; 77149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55882; 112973</t>
+          <t>56135; 113889</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13868; 32964</t>
+          <t>14258; 33855</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11869; 31231</t>
+          <t>12131; 31946</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12857; 32447</t>
+          <t>12404; 33058</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10794; 39710</t>
+          <t>9349; 38828</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10807; 28349</t>
+          <t>10381; 26672</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23254; 47485</t>
+          <t>22534; 46204</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18655; 40151</t>
+          <t>17777; 40602</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16061; 29587</t>
+          <t>14800; 29425</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28826; 55328</t>
+          <t>28510; 54379</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40068; 71693</t>
+          <t>38242; 69799</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34885; 63153</t>
+          <t>35807; 65826</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28737; 61356</t>
+          <t>27626; 62169</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>70617; 108614</t>
+          <t>70576; 106821</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>114170; 166447</t>
+          <t>117282; 167490</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81052; 122688</t>
+          <t>80122; 121868</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>164059; 241010</t>
+          <t>157256; 239591</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>101921; 142388</t>
+          <t>101559; 142806</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>163853; 220822</t>
+          <t>162886; 219087</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>119777; 171144</t>
+          <t>121848; 171702</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>231207; 317937</t>
+          <t>235759; 319722</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>178837; 234861</t>
+          <t>181139; 237608</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>295469; 369878</t>
+          <t>296390; 368209</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>213981; 276229</t>
+          <t>211384; 277284</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>430868; 543050</t>
+          <t>428459; 539202</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A13-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,99</t>
+          <t>1,02; 4,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,16</t>
+          <t>3,47; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,2</t>
+          <t>1,55; 5,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 14,34</t>
+          <t>3,19; 8,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,22</t>
+          <t>1,21; 5,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,93</t>
+          <t>4,09; 10,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,24</t>
+          <t>5,28; 12,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,74</t>
+          <t>2,73; 6,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,43</t>
+          <t>1,6; 4,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,95</t>
+          <t>4,34; 8,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,87</t>
+          <t>3,83; 7,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,53</t>
+          <t>3,4; 6,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,56</t>
+          <t>1,86; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,58</t>
+          <t>3,64; 7,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,84</t>
+          <t>1,15; 3,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,43</t>
+          <t>1,28; 4,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,57</t>
+          <t>2,43; 5,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,62</t>
+          <t>4,15; 8,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,2</t>
+          <t>0,76; 3,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,87</t>
+          <t>2,08; 4,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,11</t>
+          <t>2,59; 4,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,38</t>
+          <t>4,29; 7,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,06</t>
+          <t>1,13; 2,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,11</t>
+          <t>1,98; 3,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,61</t>
+          <t>0,61; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,15</t>
+          <t>1,69; 7,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,94</t>
+          <t>0,7; 4,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 13,69</t>
+          <t>8,12; 14,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,11</t>
+          <t>2,11; 6,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,56</t>
+          <t>2,21; 6,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,99</t>
+          <t>0,83; 4,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 19,1</t>
+          <t>13,61; 19,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,04</t>
+          <t>1,54; 4,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,9</t>
+          <t>2,55; 5,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,24</t>
+          <t>1,11; 3,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,65</t>
+          <t>11,63; 16,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,98</t>
+          <t>0,83; 4,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,6</t>
+          <t>1,05; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,48</t>
+          <t>2,7; 7,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,0</t>
+          <t>4,11; 9,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,38</t>
+          <t>2,52; 6,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,81</t>
+          <t>5,34; 10,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,38</t>
+          <t>4,97; 11,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,74</t>
+          <t>7,61; 12,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,59</t>
+          <t>2,08; 4,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,91</t>
+          <t>3,62; 7,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,26</t>
+          <t>4,38; 8,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,25</t>
+          <t>6,58; 9,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,5</t>
+          <t>0,45; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 12,39</t>
+          <t>4,55; 12,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,24</t>
+          <t>0,44; 4,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 17,78</t>
+          <t>9,39; 16,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,75</t>
+          <t>1,78; 7,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,34</t>
+          <t>3,97; 10,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,53</t>
+          <t>1,36; 6,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 24,85</t>
+          <t>16,79; 23,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,06</t>
+          <t>1,57; 4,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,77</t>
+          <t>4,96; 10,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,09</t>
+          <t>1,15; 4,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,93; 20,22</t>
+          <t>14,28; 18,96</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,07</t>
+          <t>0,74; 4,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,66</t>
+          <t>2,99; 8,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,64</t>
+          <t>1,65; 5,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 17,52</t>
+          <t>10,72; 17,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,11</t>
+          <t>2,23; 7,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,75</t>
+          <t>1,83; 6,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,85</t>
+          <t>0,9; 5,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,34</t>
+          <t>12,94; 19,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,78</t>
+          <t>1,73; 4,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,74</t>
+          <t>3,06; 6,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,51</t>
+          <t>1,67; 4,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,39</t>
+          <t>12,71; 17,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,74</t>
+          <t>1,88; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,28</t>
+          <t>2,24; 5,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,89</t>
+          <t>2,45; 5,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,71</t>
+          <t>4,24; 7,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,61</t>
+          <t>3,03; 6,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,43</t>
+          <t>3,79; 7,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,08</t>
+          <t>3,51; 7,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,03</t>
+          <t>7,26; 10,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,05</t>
+          <t>2,91; 5,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,84</t>
+          <t>3,23; 5,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,72</t>
+          <t>3,38; 5,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,73</t>
+          <t>6,28; 8,77</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,56</t>
+          <t>1,86; 4,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,12</t>
+          <t>1,5; 4,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,25</t>
+          <t>1,63; 4,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>2,38; 4,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,4</t>
+          <t>1,3; 3,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,62</t>
+          <t>2,74; 5,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,12</t>
+          <t>2,24; 4,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,56</t>
+          <t>1,9; 3,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,37</t>
+          <t>2,53; 4,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,1</t>
+          <t>2,12; 4,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,78</t>
+          <t>2,61; 4,13</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,26</t>
+          <t>2,14; 3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,9</t>
+          <t>3,4; 4,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,59</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,93</t>
+          <t>5,49; 7,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,23</t>
+          <t>3,02; 4,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,18</t>
+          <t>4,67; 6,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,84</t>
+          <t>3,36; 4,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,74</t>
+          <t>7,65; 9,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,57</t>
+          <t>2,74; 3,6</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,29</t>
+          <t>4,23; 5,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,0</t>
+          <t>3,07; 3,99</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,58</t>
+          <t>6,79; 7,9</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>30076</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2732; 13630</t>
+          <t>2778; 13444</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10429; 29488</t>
+          <t>10060; 29563</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3996; 15273</t>
+          <t>4561; 16841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11708; 44663</t>
+          <t>10181; 27642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2960; 13619</t>
+          <t>3158; 15051</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11095; 27943</t>
+          <t>11502; 30140</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13759; 35326</t>
+          <t>15256; 35182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8873; 19534</t>
+          <t>8638; 19186</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7864; 23651</t>
+          <t>8550; 23987</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26325; 51123</t>
+          <t>24820; 50335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22659; 45845</t>
+          <t>22335; 46364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22659; 51264</t>
+          <t>21566; 42489</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31035</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10274; 27393</t>
+          <t>9152; 26100</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18079; 38303</t>
+          <t>18382; 39255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5907; 19305</t>
+          <t>5801; 20001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6249; 22931</t>
+          <t>6776; 22922</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12112; 28058</t>
+          <t>12266; 29498</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21576; 45053</t>
+          <t>21677; 43003</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3986; 16732</t>
+          <t>3954; 16696</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10754; 25033</t>
+          <t>11334; 25467</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25832; 50979</t>
+          <t>25848; 48371</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44860; 75842</t>
+          <t>44123; 75210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12037; 31427</t>
+          <t>11576; 30180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21081; 42421</t>
+          <t>21323; 42763</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33349</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>58456</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89313</t>
+          <t>92474</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1942; 11500</t>
+          <t>1934; 10673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6063; 23103</t>
+          <t>5459; 22654</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2057; 12537</t>
+          <t>2220; 13036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24908; 43264</t>
+          <t>25650; 46279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6626; 20482</t>
+          <t>7061; 21438</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7641; 22364</t>
+          <t>7523; 22270</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2361; 13431</t>
+          <t>2794; 13598</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46095; 66675</t>
+          <t>48509; 70019</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10321; 26423</t>
+          <t>10057; 27072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16584; 39154</t>
+          <t>16916; 38118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7209; 21235</t>
+          <t>7261; 20963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74688; 104127</t>
+          <t>78190; 108213</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>64991</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2865; 14291</t>
+          <t>2959; 14964</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3928; 17216</t>
+          <t>3929; 17410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10108; 27681</t>
+          <t>9983; 26794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12926; 28129</t>
+          <t>15322; 33793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9476; 23716</t>
+          <t>9356; 24084</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21341; 41931</t>
+          <t>20720; 42451</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19023; 44068</t>
+          <t>19235; 43017</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23504; 51111</t>
+          <t>32099; 51468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15130; 33504</t>
+          <t>15153; 33537</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27318; 52626</t>
+          <t>27557; 53896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33612; 62581</t>
+          <t>33146; 62749</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39913; 72934</t>
+          <t>52354; 78350</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>45620</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>71342</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>894; 9147</t>
+          <t>910; 9254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10324; 26343</t>
+          <t>9680; 25649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>948; 8963</t>
+          <t>937; 8912</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17390; 31788</t>
+          <t>19311; 33290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3935; 16091</t>
+          <t>3694; 16129</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9265; 24901</t>
+          <t>8716; 23778</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2972; 14275</t>
+          <t>2972; 13455</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37130; 51852</t>
+          <t>38142; 53348</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6568; 20776</t>
+          <t>6466; 19944</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22690; 46551</t>
+          <t>21443; 44411</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5225; 17582</t>
+          <t>4935; 17229</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57847; 78347</t>
+          <t>61797; 82072</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78390</t>
+          <t>78746</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1932; 11013</t>
+          <t>2001; 11981</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7805; 23725</t>
+          <t>8201; 24493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3942; 14840</t>
+          <t>4355; 15334</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30076; 47240</t>
+          <t>29017; 47125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6181; 19767</t>
+          <t>6195; 20358</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5818; 18833</t>
+          <t>5115; 18014</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2472; 13255</t>
+          <t>2454; 13739</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33501; 49711</t>
+          <t>34127; 51160</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10230; 26254</t>
+          <t>9485; 26360</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17029; 37299</t>
+          <t>16903; 36095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8673; 24205</t>
+          <t>8967; 23580</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67242; 91612</t>
+          <t>67912; 91483</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>68706</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91198</t>
+          <t>111011</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11318; 29170</t>
+          <t>11560; 30797</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14758; 34894</t>
+          <t>14771; 35987</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16050; 38678</t>
+          <t>16070; 36712</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25509; 48122</t>
+          <t>30519; 56597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20769; 42169</t>
+          <t>19370; 39916</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25488; 51526</t>
+          <t>26274; 52294</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23479; 48960</t>
+          <t>24258; 49516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26698; 76670</t>
+          <t>56023; 83358</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36857; 63268</t>
+          <t>36532; 64056</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44423; 79063</t>
+          <t>43782; 76892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44073; 77149</t>
+          <t>45606; 76778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56135; 113889</t>
+          <t>93657; 130833</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>22057</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>53418</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14258; 33855</t>
+          <t>13826; 31817</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12131; 31946</t>
+          <t>11614; 31058</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12404; 33058</t>
+          <t>12704; 33795</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9349; 38828</t>
+          <t>18978; 38691</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10381; 26672</t>
+          <t>10189; 27824</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22534; 46204</t>
+          <t>22520; 46903</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17777; 40602</t>
+          <t>17773; 40560</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14800; 29425</t>
+          <t>18576; 33551</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28510; 54379</t>
+          <t>29029; 53415</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38242; 69799</t>
+          <t>40362; 70855</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35807; 65826</t>
+          <t>34097; 64806</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>27626; 62169</t>
+          <t>42438; 67165</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>70576; 106821</t>
+          <t>70173; 105971</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>117282; 167490</t>
+          <t>116213; 165627</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80122; 121868</t>
+          <t>82159; 123631</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157256; 239591</t>
+          <t>193771; 249185</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>101559; 142806</t>
+          <t>102113; 142944</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>162886; 219087</t>
+          <t>165743; 220736</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>121848; 171702</t>
+          <t>119203; 171138</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>235759; 319722</t>
+          <t>285399; 338445</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>181139; 237608</t>
+          <t>182237; 239500</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>296390; 368209</t>
+          <t>294840; 368516</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>211384; 277284</t>
+          <t>213192; 277135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>428459; 539202</t>
+          <t>493532; 573701</t>
         </is>
       </c>
     </row>
